--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C35" s="16" t="n"/>
       <c r="D35" s="16" t="n"/>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C36" s="16" t="n"/>
       <c r="D36" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" s="16" t="n"/>
       <c r="D35" s="16" t="n"/>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" s="16" t="n"/>
       <c r="D36" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>
